--- a/experiments/results/densenet101/CIFAR-10/baseline/msp/adaptive/avg/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-10/baseline/msp/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -762,6 +762,104 @@
         <v>95.33</v>
       </c>
       <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.2,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>94.48</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>94.51000000000001</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>93.72</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.2,type=avg</t>
         </is>
